--- a/output/2025_A24_SECCION_E_TABLAS.xlsx
+++ b/output/2025_A24_SECCION_E_TABLAS.xlsx
@@ -159,7 +159,7 @@
     <t>Hospital San José (Melipilla)</t>
   </si>
   <si>
-    <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+    <t>Hospital San Juan de Dios (Santiago)</t>
   </si>
   <si>
     <t>Hospital de Peñaflor</t>
